--- a/Data/Excel/tower_level.xlsx
+++ b/Data/Excel/tower_level.xlsx
@@ -400,10 +400,10 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>100101</v>
+        <v>30110001</v>
       </c>
       <c r="C5">
-        <v>1001</v>
+        <v>30100001</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -412,13 +412,13 @@
         <v>41</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -453,10 +453,10 @@
         <v>40</v>
       </c>
       <c r="B6">
-        <v>100102</v>
+        <v>30110002</v>
       </c>
       <c r="C6">
-        <v>1001</v>
+        <v>30100001</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -465,13 +465,13 @@
         <v>41</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G6">
         <v>100</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I6">
         <v>120</v>
@@ -506,10 +506,10 @@
         <v>40</v>
       </c>
       <c r="B7">
-        <v>100103</v>
+        <v>30110003</v>
       </c>
       <c r="C7">
-        <v>1001</v>
+        <v>30100001</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -518,13 +518,13 @@
         <v>41</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G7">
         <v>100</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I7">
         <v>180</v>
@@ -559,10 +559,10 @@
         <v>40</v>
       </c>
       <c r="B8">
-        <v>100201</v>
+        <v>30110004</v>
       </c>
       <c r="C8">
-        <v>1002</v>
+        <v>30100002</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -571,13 +571,13 @@
         <v>44</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G8">
         <v>180</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -612,10 +612,10 @@
         <v>40</v>
       </c>
       <c r="B9">
-        <v>100202</v>
+        <v>30110005</v>
       </c>
       <c r="C9">
-        <v>1002</v>
+        <v>30100002</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -624,13 +624,13 @@
         <v>44</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G9">
         <v>180</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I9">
         <v>200</v>
@@ -665,10 +665,10 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>100203</v>
+        <v>30110006</v>
       </c>
       <c r="C10">
-        <v>1002</v>
+        <v>30100002</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -677,13 +677,13 @@
         <v>44</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G10">
         <v>180</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I10">
         <v>300</v>
@@ -718,10 +718,10 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>100301</v>
+        <v>30110007</v>
       </c>
       <c r="C11">
-        <v>1003</v>
+        <v>30100003</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -730,13 +730,13 @@
         <v>44</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G11">
         <v>150</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>46</v>
       </c>
       <c r="P11">
-        <v>1003</v>
+        <v>50000003</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -771,10 +771,10 @@
         <v>40</v>
       </c>
       <c r="B12">
-        <v>100302</v>
+        <v>30110008</v>
       </c>
       <c r="C12">
-        <v>1003</v>
+        <v>30100003</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -783,13 +783,13 @@
         <v>44</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G12">
         <v>150</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I12">
         <v>160</v>
@@ -813,7 +813,7 @@
         <v>46</v>
       </c>
       <c r="P12">
-        <v>1003</v>
+        <v>50000003</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
@@ -824,10 +824,10 @@
         <v>40</v>
       </c>
       <c r="B13">
-        <v>100303</v>
+        <v>30110009</v>
       </c>
       <c r="C13">
-        <v>1003</v>
+        <v>30100003</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -836,13 +836,13 @@
         <v>44</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G13">
         <v>150</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I13">
         <v>240</v>
@@ -866,7 +866,7 @@
         <v>46</v>
       </c>
       <c r="P13">
-        <v>1003</v>
+        <v>50000003</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -877,10 +877,10 @@
         <v>40</v>
       </c>
       <c r="B14">
-        <v>100401</v>
+        <v>30110010</v>
       </c>
       <c r="C14">
-        <v>1004</v>
+        <v>30100004</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -889,13 +889,13 @@
         <v>44</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G14">
         <v>150</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -930,10 +930,10 @@
         <v>40</v>
       </c>
       <c r="B15">
-        <v>100402</v>
+        <v>30110011</v>
       </c>
       <c r="C15">
-        <v>1004</v>
+        <v>30100004</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -942,13 +942,13 @@
         <v>44</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G15">
         <v>150</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I15">
         <v>160</v>
@@ -983,10 +983,10 @@
         <v>40</v>
       </c>
       <c r="B16">
-        <v>100403</v>
+        <v>30110012</v>
       </c>
       <c r="C16">
-        <v>1004</v>
+        <v>30100004</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -995,13 +995,13 @@
         <v>44</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G16">
         <v>150</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I16">
         <v>240</v>
@@ -1036,10 +1036,10 @@
         <v>40</v>
       </c>
       <c r="B17">
-        <v>100501</v>
+        <v>30110013</v>
       </c>
       <c r="C17">
-        <v>1005</v>
+        <v>30100005</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1048,13 +1048,13 @@
         <v>44</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G17">
         <v>150</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>100502</v>
+        <v>30110014</v>
       </c>
       <c r="C18">
-        <v>1005</v>
+        <v>30100005</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1101,13 +1101,13 @@
         <v>44</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G18">
         <v>150</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I18">
         <v>160</v>
@@ -1142,10 +1142,10 @@
         <v>40</v>
       </c>
       <c r="B19">
-        <v>100503</v>
+        <v>30110015</v>
       </c>
       <c r="C19">
-        <v>1005</v>
+        <v>30100005</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1154,13 +1154,13 @@
         <v>44</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="G19">
         <v>150</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>20000003</v>
       </c>
       <c r="I19">
         <v>240</v>
